--- a/src/main/resources/static/template_exel/personnels/template_import_personnels_complet.xlsx
+++ b/src/main/resources/static/template_exel/personnels/template_import_personnels_complet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="RolesPersonnels" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t xml:space="preserve">libelle</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t xml:space="preserve">commentaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datePaie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prime</t>
   </si>
 </sst>
 </file>
@@ -378,9 +387,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
